--- a/artfynd/A 12968-2024 artfynd.xlsx
+++ b/artfynd/A 12968-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110533293</v>
+        <v>110511078</v>
       </c>
       <c r="B2" t="n">
-        <v>103838</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651779.8369138315</v>
+        <v>651706</v>
       </c>
       <c r="R2" t="n">
-        <v>6555483.005413858</v>
+        <v>6555491</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +744,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>8b9f0878-0796-4759-8ef3-759d96a2f6b5</t>
+          <t>906fc069-469b-4ad4-a579-fcbf92c41535</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -757,24 +752,14 @@
           <t>2023-04-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-04-28</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>203.</t>
+          <t>Nr323.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110534518</v>
+        <v>110533293</v>
       </c>
       <c r="B3" t="n">
-        <v>103838</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -849,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651813.1723192683</v>
+        <v>651780</v>
       </c>
       <c r="R3" t="n">
-        <v>6555473.534543036</v>
+        <v>6555483</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,7 +859,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>9a515b27-ed77-40a4-ac2e-a34783bfd108</t>
+          <t>8b9f0878-0796-4759-8ef3-759d96a2f6b5</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -887,24 +867,14 @@
           <t>2023-04-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-04-28</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Nr200. Kapad.</t>
+          <t>203.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,6 +898,466 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>110534478</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Södertälje kommun, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>651902</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6555431</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ytterjärna</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>e299b83e-35f9-4251-9447-9ac45e0f9a51</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Nr346.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Julia Stigenberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Miguel Jaramillo</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>110534481</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Södertälje kommun, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>651853</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6555447</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ytterjärna</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>9f9ae69c-74a9-4051-b136-c05b922ef2ef</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Nr340.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Julia Stigenberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Miguel Jaramillo</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>110534482</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Södertälje kommun, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>651841</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6555452</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ytterjärna</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>bc4d7942-8d1f-443e-8149-6d6eaae3b7bf</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Nr339.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Julia Stigenberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Miguel Jaramillo</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>110534518</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Södertälje kommun, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>651813</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6555473</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ytterjärna</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>9a515b27-ed77-40a4-ac2e-a34783bfd108</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Nr200. Kapad.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Julia Stigenberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Miguel Jaramillo</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Skyddsvärda träd</t>
         </is>

--- a/artfynd/A 12968-2024 artfynd.xlsx
+++ b/artfynd/A 12968-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110511078</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110533293</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110534478</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110534481</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110534482</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1362,8 +1392,21 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110534518</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>